--- a/ProjectReports/Gant Table.xlsx
+++ b/ProjectReports/Gant Table.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{2566B9CB-C597-4B75-8D11-821E0E8CA690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6278F261-76AB-41C0-A385-933E7EBB5E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,6 +885,9 @@
     <xf numFmtId="178" fontId="27" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -902,9 +905,6 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1397,60 +1397,60 @@
         <v>1</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="27"/>
+      <c r="K2" s="21"/>
       <c r="L2" s="28"/>
       <c r="M2" s="29"/>
       <c r="N2" s="9"/>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="21" t="s">
         <v>6</v>
       </c>
       <c r="P2" s="28"/>
       <c r="Q2" s="28"/>
       <c r="R2" s="29"/>
       <c r="S2" s="10"/>
-      <c r="T2" s="27" t="s">
+      <c r="T2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
       <c r="W2" s="30"/>
       <c r="X2" s="11"/>
-      <c r="Y2" s="27" t="s">
+      <c r="Y2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
       <c r="AC2" s="30"/>
       <c r="AD2" s="12"/>
-      <c r="AE2" s="27" t="s">
+      <c r="AE2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21"/>
-      <c r="AK2" s="21"/>
-      <c r="AL2" s="21"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="22"/>
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="22"/>
     </row>
     <row r="3" spans="2:67" s="16" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="13" t="s">
@@ -1477,12 +1477,12 @@
       <c r="AA3" s="15"/>
     </row>
     <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="23"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="20">
         <v>1</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="19">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -1721,7 +1721,7 @@
         <v>5</v>
       </c>
       <c r="G7" s="19">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="2:67" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1741,7 +1741,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="19">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" spans="2:67" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1761,7 +1761,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="19">
-        <v>0.4</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="10" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="19">
-        <v>0</v>
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectReports/Gant Table.xlsx
+++ b/ProjectReports/Gant Table.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6278F261-76AB-41C0-A385-933E7EBB5E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656A07AA-4E83-4CED-827C-6D5EDE8371B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve"> 周期突出显示：</t>
   </si>
@@ -120,6 +120,9 @@
   <si>
     <t>data analysis</t>
     <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plan using period</t>
   </si>
 </sst>
 </file>
@@ -129,9 +132,9 @@
   <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_ &quot;¥&quot;* #,##0_ ;_ &quot;¥&quot;* \-#,##0_ ;_ &quot;¥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="#,##0_ "/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0_ "/>
   </numFmts>
   <fonts count="31" x14ac:knownFonts="1">
     <font>
@@ -780,8 +783,8 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -882,7 +885,7 @@
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="27" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
@@ -917,64 +920,64 @@
     </xf>
   </cellXfs>
   <cellStyles count="58">
-    <cellStyle name="20% - 着色 1" xfId="35" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="39" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="43" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="47" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="51" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="55" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="36" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="40" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="44" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="48" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="52" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="56" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="37" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="41" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="45" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="49" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="53" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="57" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="百分比" xfId="22" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="35" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="39" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="43" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="47" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="51" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="55" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="36" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="40" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="44" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="48" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="52" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="56" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="37" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="41" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="45" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="49" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="53" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="57" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="34" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="38" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="42" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="46" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="50" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="54" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="24" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="28" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="30" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3" customBuiltin="1"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6" customBuiltin="1"/>
+    <cellStyle name="Currency" xfId="20" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Currency [0]" xfId="21" builtinId="7" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="12" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="23" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="1" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="9" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="10" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="11" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="26" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="29" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="25" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="32" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="27" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="22" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="33" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="31" builtinId="11" customBuiltin="1"/>
     <cellStyle name="标签" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="标题" xfId="8" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="1" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="9" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="10" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="11" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="24" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="好" xfId="23" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="33" builtinId="25" customBuiltin="1"/>
     <cellStyle name="活动" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="货币" xfId="20" builtinId="4" customBuiltin="1"/>
-    <cellStyle name="货币[0]" xfId="21" builtinId="7" customBuiltin="1"/>
     <cellStyle name="计划图例" xfId="14" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="计算" xfId="28" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="30" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="12" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="31" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="千位分隔" xfId="18" builtinId="3" customBuiltin="1"/>
-    <cellStyle name="千位分隔[0]" xfId="19" builtinId="6" customBuiltin="1"/>
     <cellStyle name="实际（超出计划）图例" xfId="16" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="实际图例" xfId="15" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="适中" xfId="25" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="27" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="26" builtinId="20" customBuiltin="1"/>
     <cellStyle name="完成（超出计划）百分比图例" xfId="17" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="完成百分比" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="项目标题" xfId="4" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="着色 1" xfId="34" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="38" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="42" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="46" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="50" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="54" builtinId="49" customBuiltin="1"/>
     <cellStyle name="周期标题" xfId="3" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="周期突出显示控件" xfId="7" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
     <cellStyle name="周期值" xfId="13" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="注释" xfId="32" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -1397,7 +1400,9 @@
         <v>1</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="21"/>
+      <c r="K2" s="21" t="s">
+        <v>20</v>
+      </c>
       <c r="L2" s="28"/>
       <c r="M2" s="29"/>
       <c r="N2" s="9"/>
@@ -1701,7 +1706,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -1721,7 +1726,7 @@
         <v>5</v>
       </c>
       <c r="G7" s="19">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:67" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1761,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="19">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -1781,7 +1786,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -1792,16 +1797,16 @@
         <v>13</v>
       </c>
       <c r="D11" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="18">
         <v>13</v>
       </c>
       <c r="F11" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="19">
-        <v>0.78</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
